--- a/backend/main.xlsx
+++ b/backend/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kumaran\Desktop\flutter_projects\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{565F9424-2545-4E5D-BAA6-384D96EC5F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4282E83-56F6-4E4B-9C4F-FC07DDB5E45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -117,7 +116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -148,12 +147,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -161,18 +154,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -186,19 +173,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -423,6 +407,7 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -451,15 +436,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="3">
-        <v>789456123</v>
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>9490840378</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>_xlfn.CONCAT(B2,"@gmail.com")</f>
         <v>kumaran@gmail.com</v>
       </c>
       <c r="E2" s="1" t="str">
-        <f t="shared" ref="E2:E16" si="0">_xlfn.SINGLE(_xlfn.CONCAT(B2,C2))</f>
-        <v>kumaran789456123</v>
+        <f t="shared" ref="E2:E16" ca="1" si="0">_xlfn.SINGLE(_xlfn.CONCAT(B2,C2))</f>
+        <v>kumaran9490840378</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -469,16 +455,17 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4">
-        <v>789456121</v>
+      <c r="C3" s="3">
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>9149527293</v>
       </c>
       <c r="D3" s="1" t="str">
         <f>_xlfn.CONCAT(B3,"@gmail.com")</f>
         <v>leena@gmail.com</v>
       </c>
       <c r="E3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>leena789456121</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>leena9149527293</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -488,17 +475,17 @@
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4">
-        <f t="shared" ref="C4:C16" ca="1" si="1">INT(RAND()*10000000000)</f>
-        <v>3930381677</v>
+      <c r="C4" s="3">
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>4091898454</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f t="shared" ref="D4:D15" si="2">_xlfn.SINGLE(_xlfn.CONCAT(B4,"@gmail.com"))</f>
+        <f t="shared" ref="D4:D15" si="1">_xlfn.SINGLE(_xlfn.CONCAT(B4,"@gmail.com"))</f>
         <v>virat@gmail.com</v>
       </c>
       <c r="E4" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>virat3930381677</v>
+        <v>virat4091898454</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -508,17 +495,17 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>8032097169</v>
+      <c r="C5" s="3">
+        <f t="shared" ref="C3:C16" ca="1" si="2">INT(RAND()*10000000000)</f>
+        <v>9532025982</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>yamini@gmail.com</v>
       </c>
       <c r="E5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>yamini8032097169</v>
+        <v>yamini9532025982</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -528,17 +515,17 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>3860709964</v>
+      <c r="C6" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>4275427668</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>bala@gmail.com</v>
       </c>
       <c r="E6" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bala3860709964</v>
+        <v>bala4275427668</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -548,17 +535,17 @@
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>4881220456</v>
+      <c r="C7" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>6767548145</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>murugan@gmail.com</v>
       </c>
       <c r="E7" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>murugan4881220456</v>
+        <v>murugan6767548145</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -568,17 +555,17 @@
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>4114112514</v>
+      <c r="C8" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>2074930587</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>vani@gmail.com</v>
       </c>
       <c r="E8" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>vani4114112514</v>
+        <v>vani2074930587</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -588,17 +575,17 @@
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>2079350735</v>
+      <c r="C9" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>8101411405</v>
       </c>
       <c r="D9" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>ram@gmail.com</v>
       </c>
       <c r="E9" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ram2079350735</v>
+        <v>ram8101411405</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -608,17 +595,17 @@
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>5619565727</v>
+      <c r="C10" s="3">
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>6571612588</v>
       </c>
       <c r="D10" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>rocky@gmail.com</v>
       </c>
       <c r="E10" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>rocky5619565727</v>
+        <v>rocky6571612588</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -628,17 +615,17 @@
       <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>1274128235</v>
+      <c r="C11" s="3">
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>2424310905</v>
       </c>
       <c r="D11" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>rakesh@gmail.com</v>
       </c>
       <c r="E11" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>rakesh1274128235</v>
+        <v>rakesh2424310905</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -648,17 +635,17 @@
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>5188543034</v>
+      <c r="C12" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>8867930907</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>anu@gmail.com</v>
       </c>
       <c r="E12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>anu5188543034</v>
+        <v>anu8867930907</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -668,17 +655,17 @@
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>9414442248</v>
+      <c r="C13" s="3">
+        <f ca="1">INT(RAND()*10000000000)</f>
+        <v>4794007180</v>
       </c>
       <c r="D13" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>anupama@gmail.com</v>
       </c>
       <c r="E13" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>anupama9414442248</v>
+        <v>anupama4794007180</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -688,17 +675,17 @@
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>6124418985</v>
+      <c r="C14" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>8960114775</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>dhivya@gmail.com</v>
       </c>
       <c r="E14" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>dhivya6124418985</v>
+        <v>dhivya8960114775</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -708,17 +695,17 @@
       <c r="B15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>5812321377</v>
+      <c r="C15" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>1900197262</v>
       </c>
       <c r="D15" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>raju@gmail.com</v>
       </c>
       <c r="E15" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>raju5812321377</v>
+        <v>raju1900197262</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -728,9 +715,9 @@
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>5382240378</v>
+      <c r="C16" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>4214306474</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.CONCAT(B16,"@gmail.com")</f>
@@ -738,7 +725,7 @@
       </c>
       <c r="E16" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>rahul5382240378</v>
+        <v>rahul4214306474</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +743,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -768,10 +755,10 @@
       <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -791,7 +778,7 @@
       <c r="E2" s="1">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -811,7 +798,7 @@
       <c r="E3" s="2">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -831,7 +818,7 @@
       <c r="E4" s="1">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -851,7 +838,7 @@
       <c r="E5" s="1">
         <v>15</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -871,7 +858,7 @@
       <c r="E6" s="1">
         <v>16</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -891,7 +878,7 @@
       <c r="E7" s="1">
         <v>17</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -911,7 +898,7 @@
       <c r="E8" s="1">
         <v>12</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -931,7 +918,7 @@
       <c r="E9" s="1">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -951,7 +938,7 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -971,7 +958,7 @@
       <c r="E11" s="1">
         <v>5</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -991,7 +978,7 @@
       <c r="E12" s="1">
         <v>7</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       <c r="E13" s="1">
         <v>8</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1031,7 +1018,7 @@
       <c r="E14" s="1">
         <v>9</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1051,7 +1038,7 @@
       <c r="E15" s="1">
         <v>10</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1071,7 +1058,7 @@
       <c r="E16" s="1">
         <v>15</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1091,7 +1078,7 @@
       <c r="E17" s="1">
         <v>12</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1111,7 +1098,7 @@
       <c r="E18" s="2">
         <v>13</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1131,7 +1118,7 @@
       <c r="E19" s="1">
         <v>14</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1151,7 +1138,7 @@
       <c r="E20" s="1">
         <v>15</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1171,7 +1158,7 @@
       <c r="E21" s="1">
         <v>16</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1191,7 +1178,7 @@
       <c r="E22" s="1">
         <v>17</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1211,7 +1198,7 @@
       <c r="E23" s="1">
         <v>12</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1231,7 +1218,7 @@
       <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1251,7 +1238,7 @@
       <c r="E25" s="1">
         <v>3</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1271,7 +1258,7 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1291,7 +1278,7 @@
       <c r="E27" s="1">
         <v>7</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1311,7 +1298,7 @@
       <c r="E28" s="1">
         <v>8</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1331,7 +1318,7 @@
       <c r="E29" s="1">
         <v>9</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1351,7 +1338,7 @@
       <c r="E30" s="1">
         <v>10</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1371,7 +1358,7 @@
       <c r="E31" s="1">
         <v>16</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>25</v>
       </c>
     </row>
